--- a/resources/mail.xlsx
+++ b/resources/mail.xlsx
@@ -2015,16 +2015,16 @@
     </row>
     <row r="25" ht="13.5" customHeight="1" s="8">
       <c r="A25" s="4" t="n">
-        <v>99002</v>
+        <v>30060</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>测试邮件</t>
+          <t>星陨石已收</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>这是测试</t>
+          <t>道友已拾回星陨石，赏赐随信附上</t>
         </is>
       </c>
       <c r="X25" s="15" t="n"/>
@@ -2034,7 +2034,11 @@
       <c r="AJ25" s="15" t="n"/>
     </row>
     <row r="26" ht="13.5" customHeight="1" s="8">
-      <c r="A26" s="4" t="n"/>
+      <c r="A26" s="4" t="n">
+        <v>30061</v>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="X26" s="15" t="n"/>
       <c r="AA26" s="15" t="n"/>
       <c r="AD26" s="15" t="n"/>
@@ -2190,7 +2194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="15.125" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -2394,43 +2398,61 @@
     </row>
     <row r="6" ht="16.5" customHeight="1" s="8">
       <c r="A6" s="19" t="n">
-        <v>99</v>
-      </c>
-      <c r="B6" s="19" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B6" s="19" t="n"/>
       <c r="C6" s="19" t="n">
-        <v>99002</v>
+        <v>30060</v>
       </c>
       <c r="D6" s="19" t="n"/>
       <c r="E6" s="19" t="n"/>
       <c r="F6" s="20" t="n"/>
       <c r="G6" s="20" t="n"/>
-      <c r="H6" s="19" t="inlineStr">
-        <is>
-          <t>系统</t>
-        </is>
-      </c>
-      <c r="I6" s="19" t="n"/>
+      <c r="H6" s="19" t="n"/>
+      <c r="I6" s="19" t="n">
+        <v>10100</v>
+      </c>
       <c r="J6" s="19" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="n"/>
-      <c r="B7" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="25" t="n"/>
+      <c r="A7" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" s="25" t="n"/>
+      <c r="C7" s="25" t="n">
+        <v>30061</v>
+      </c>
       <c r="D7" s="25" t="n"/>
       <c r="E7" s="25" t="n"/>
-      <c r="F7" s="25" t="n"/>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>2025-01-01 00:00:00</t>
+        </is>
+      </c>
       <c r="G7" s="25" t="n"/>
-      <c r="H7" s="25" t="inlineStr">
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n">
+        <v>10099</v>
+      </c>
+      <c r="J7" s="25" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="n"/>
+      <c r="B8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="25" t="n"/>
+      <c r="D8" s="25" t="n"/>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="25" t="n"/>
+      <c r="G8" s="25" t="n"/>
+      <c r="H8" s="25" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="I7" s="25" t="n"/>
-      <c r="J7" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
+      <c r="J8" s="25" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B2 A3 A4:B4">

--- a/resources/mail.xlsx
+++ b/resources/mail.xlsx
@@ -2034,7 +2034,19 @@
       <c r="AJ25" s="15" t="n"/>
     </row>
     <row r="26" ht="13.5" customHeight="1" s="8">
-      <c r="A26" s="4" t="n"/>
+      <c r="A26" s="4" t="n">
+        <v>30018</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>太虚剑宗开宗立派</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>太虚剑宗今日开宗，广纳天下英才，共证剑道</t>
+        </is>
+      </c>
       <c r="X26" s="15" t="n"/>
       <c r="AA26" s="15" t="n"/>
       <c r="AD26" s="15" t="n"/>

--- a/resources/mail.xlsx
+++ b/resources/mail.xlsx
@@ -2054,7 +2054,19 @@
       <c r="AJ26" s="15" t="n"/>
     </row>
     <row r="27" ht="13.5" customHeight="1" s="8">
-      <c r="A27" s="4" t="n"/>
+      <c r="A27" s="4" t="n">
+        <v>30019</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>太虚剑宗开宗立派</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>太虚剑宗今日开宗，广纳天下英才，共证剑道</t>
+        </is>
+      </c>
       <c r="X27" s="15" t="n"/>
       <c r="AA27" s="15" t="n"/>
       <c r="AD27" s="15" t="n"/>

--- a/resources/mail.xlsx
+++ b/resources/mail.xlsx
@@ -2074,7 +2074,19 @@
       <c r="AJ27" s="15" t="n"/>
     </row>
     <row r="28" ht="13.5" customHeight="1" s="8">
-      <c r="A28" s="4" t="n"/>
+      <c r="A28" s="4" t="n">
+        <v>30020</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>太虚剑宗开宗立派</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>太虚剑宗今日开宗，广纳天下英才，共证剑道</t>
+        </is>
+      </c>
       <c r="X28" s="15" t="n"/>
       <c r="AA28" s="15" t="n"/>
       <c r="AD28" s="15" t="n"/>

--- a/resources/mail.xlsx
+++ b/resources/mail.xlsx
@@ -2034,7 +2034,15 @@
       <c r="AJ25" s="15" t="n"/>
     </row>
     <row r="26" ht="13.5" customHeight="1" s="8">
-      <c r="A26" s="4" t="n"/>
+      <c r="A26" s="4" t="n">
+        <v>30101</v>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>中秋快乐</t>
+        </is>
+      </c>
       <c r="X26" s="15" t="n"/>
       <c r="AA26" s="15" t="n"/>
       <c r="AD26" s="15" t="n"/>
@@ -2190,7 +2198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="15.125" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -2411,22 +2419,40 @@
       <c r="J6" s="19" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="n"/>
-      <c r="B7" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="25" t="n"/>
+      <c r="A7" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B7" s="25" t="n"/>
+      <c r="C7" s="25" t="n">
+        <v>30101</v>
+      </c>
       <c r="D7" s="25" t="n"/>
       <c r="E7" s="25" t="n"/>
       <c r="F7" s="25" t="n"/>
       <c r="G7" s="25" t="n"/>
-      <c r="H7" s="25" t="inlineStr">
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n">
+        <v>100900</v>
+      </c>
+      <c r="J7" s="25" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="n"/>
+      <c r="B8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="25" t="n"/>
+      <c r="D8" s="25" t="n"/>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="25" t="n"/>
+      <c r="G8" s="25" t="n"/>
+      <c r="H8" s="25" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="I7" s="25" t="n"/>
-      <c r="J7" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
+      <c r="J8" s="25" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B2 A3 A4:B4">

--- a/resources/mail.xlsx
+++ b/resources/mail.xlsx
@@ -2015,16 +2015,16 @@
     </row>
     <row r="25" ht="13.5" customHeight="1" s="8">
       <c r="A25" s="4" t="n">
-        <v>30100</v>
+        <v>30101</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>冰雪节结束补偿</t>
+          <t>中秋祝福</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>亲爱的玩家，冰雪节已落幕，奉上补偿请查收</t>
+          <t>中秋快乐</t>
         </is>
       </c>
       <c r="X25" s="15" t="n"/>
@@ -2035,9 +2035,13 @@
     </row>
     <row r="26" ht="13.5" customHeight="1" s="8">
       <c r="A26" s="4" t="n">
-        <v>30101</v>
-      </c>
-      <c r="B26" s="3" t="n"/>
+        <v>30102</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>中秋祝福</t>
+        </is>
+      </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
           <t>中秋快乐</t>
@@ -2050,7 +2054,19 @@
       <c r="AJ26" s="15" t="n"/>
     </row>
     <row r="27" ht="13.5" customHeight="1" s="8">
-      <c r="A27" s="4" t="n"/>
+      <c r="A27" s="4" t="n">
+        <v>30103</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>中秋祝福</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>中秋快乐</t>
+        </is>
+      </c>
       <c r="X27" s="15" t="n"/>
       <c r="AA27" s="15" t="n"/>
       <c r="AD27" s="15" t="n"/>
@@ -2058,7 +2074,19 @@
       <c r="AJ27" s="15" t="n"/>
     </row>
     <row r="28" ht="13.5" customHeight="1" s="8">
-      <c r="A28" s="4" t="n"/>
+      <c r="A28" s="4" t="n">
+        <v>30104</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>中秋祝福</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>中秋快乐</t>
+        </is>
+      </c>
       <c r="X28" s="15" t="n"/>
       <c r="AA28" s="15" t="n"/>
       <c r="AD28" s="15" t="n"/>
@@ -2198,7 +2226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="15.125" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -2402,25 +2430,25 @@
     </row>
     <row r="6" ht="16.5" customHeight="1" s="8">
       <c r="A6" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="19" t="n">
-        <v>3</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B6" s="19" t="n"/>
       <c r="C6" s="19" t="n">
-        <v>30100</v>
+        <v>30101</v>
       </c>
       <c r="D6" s="19" t="n"/>
       <c r="E6" s="19" t="n"/>
       <c r="F6" s="20" t="n"/>
       <c r="G6" s="20" t="n"/>
       <c r="H6" s="19" t="n"/>
-      <c r="I6" s="19" t="n"/>
+      <c r="I6" s="19" t="n">
+        <v>100900</v>
+      </c>
       <c r="J6" s="19" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="25" t="n"/>
       <c r="C7" s="25" t="n">
@@ -2437,22 +2465,80 @@
       <c r="J7" s="25" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="n"/>
-      <c r="B8" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="25" t="n"/>
+      <c r="A8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" s="25" t="n"/>
+      <c r="C8" s="25" t="n">
+        <v>30103</v>
+      </c>
       <c r="D8" s="25" t="n"/>
       <c r="E8" s="25" t="n"/>
       <c r="F8" s="25" t="n"/>
       <c r="G8" s="25" t="n"/>
-      <c r="H8" s="25" t="inlineStr">
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n">
+        <v>100900</v>
+      </c>
+      <c r="J8" s="25" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B9" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>30101</v>
+      </c>
+      <c r="D9" s="25" t="n"/>
+      <c r="E9" s="25" t="n"/>
+      <c r="F9" s="25" t="n"/>
+      <c r="G9" s="25" t="n"/>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="25" t="n">
+        <v>100900</v>
+      </c>
+      <c r="J9" s="25" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>30101</v>
+      </c>
+      <c r="D10" s="25" t="n"/>
+      <c r="E10" s="25" t="n"/>
+      <c r="F10" s="25" t="n"/>
+      <c r="G10" s="25" t="n"/>
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="25" t="n">
+        <v>100900</v>
+      </c>
+      <c r="J10" s="25" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="n"/>
+      <c r="B11" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="25" t="n"/>
+      <c r="D11" s="25" t="n"/>
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="25" t="n"/>
+      <c r="G11" s="25" t="n"/>
+      <c r="H11" s="25" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="I8" s="25" t="n"/>
-      <c r="J8" s="25" t="n"/>
+      <c r="I11" s="25" t="n"/>
+      <c r="J11" s="25" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B2 A3 A4:B4">
